--- a/converted/oylik/2026-08/Elektr Murojaatlar.xlsx
+++ b/converted/oylik/2026-08/Elektr Murojaatlar.xlsx
@@ -11,11 +11,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="111">
   <si>
     <t>Murojaatlar Avgust Holatiga Ko'ra</t>
   </si>
   <si>
+    <t>Podstansiya</t>
+  </si>
+  <si>
+    <t>Fider</t>
+  </si>
+  <si>
     <t>TP Nomi</t>
   </si>
   <si>
@@ -52,9 +58,18 @@
     <t>Ma'sul xodim (manba)</t>
   </si>
   <si>
+    <t>Eslatma</t>
+  </si>
+  <si>
     <t>Manba (fayl, qator)</t>
   </si>
   <si>
+    <t>Baliqchi</t>
+  </si>
+  <si>
+    <t>Oqqo'rg'on</t>
+  </si>
+  <si>
     <t>665</t>
   </si>
   <si>
@@ -91,6 +106,9 @@
     <t>Afsona MFY</t>
   </si>
   <si>
+    <t>TP 405 shu hududning Transformatorlar fayllarida ham, abonentlar reestrida ham yo'q - TP ga bog'lanmaydi</t>
+  </si>
+  <si>
     <t>baliqchi/7 oylik/Elektr Murojaatlar.xlsx, 18-qator; baliqchi/Avgust/Elektr Murojaatlar.xlsx, 10-qator</t>
   </si>
   <si>
@@ -103,6 +121,9 @@
     <t>Sahovat MFY</t>
   </si>
   <si>
+    <t>TP 515 shu hududning Transformatorlar fayllarida ham, abonentlar reestrida ham yo'q - TP ga bog'lanmaydi</t>
+  </si>
+  <si>
     <t>baliqchi/7 oylik/Elektr Murojaatlar.xlsx, 12-qator; baliqchi/Avgust/Elektr Murojaatlar.xlsx, 4-qator</t>
   </si>
   <si>
@@ -124,6 +145,9 @@
     <t>baliqchi/7 oylik/Elektr Murojaatlar.xlsx, 13-qator; baliqchi/Avgust/Elektr Murojaatlar.xlsx, 5-qator</t>
   </si>
   <si>
+    <t>Sarkor</t>
+  </si>
+  <si>
     <t>246</t>
   </si>
   <si>
@@ -163,6 +187,9 @@
     <t>770392757</t>
   </si>
   <si>
+    <t>TP o'rnida "Yangi" yozilgan - TP bo'sh qoldirildi</t>
+  </si>
+  <si>
     <t>baliqchi/7 oylik/Elektr Murojaatlar.xlsx, 16-qator; baliqchi/Avgust/Elektr Murojaatlar.xlsx, 8-qator</t>
   </si>
   <si>
@@ -181,9 +208,18 @@
     <t>Alchazor MFY</t>
   </si>
   <si>
+    <t>TP 222 shu hududning Transformatorlar fayllarida yo'q - TP bo'sh qoldirildi</t>
+  </si>
+  <si>
     <t>baliqchi/7 oylik/Elektr Murojaatlar.xlsx, 17-qator; baliqchi/Avgust/Elektr Murojaatlar.xlsx, 9-qator</t>
   </si>
   <si>
+    <t>Qo'shtepasaroy</t>
+  </si>
+  <si>
+    <t>Qaxramon</t>
+  </si>
+  <si>
     <t>282</t>
   </si>
   <si>
@@ -226,9 +262,15 @@
     <t>Tovuldi MFY, Tovuldi koʼchasi, 18-uy</t>
   </si>
   <si>
+    <t>TP 287 Transformatorlar faylida boshqa fiderda (Chinobod / Xaqulobod), murojaatda Qaxramon - TP bog'lanmaydi</t>
+  </si>
+  <si>
     <t>chinobod/Elektr Murojaatlar.xlsx [Avgust], 4-qator</t>
   </si>
   <si>
+    <t>Sirmoq</t>
+  </si>
+  <si>
     <t>117</t>
   </si>
   <si>
@@ -275,6 +317,12 @@
   </si>
   <si>
     <t>chinobod/Elektr Murojaatlar.xlsx [Avgust], 6-qator</t>
+  </si>
+  <si>
+    <t>Chinobod</t>
+  </si>
+  <si>
+    <t>Xaqulobod</t>
   </si>
   <si>
     <t>171</t>
@@ -713,17 +761,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="14" style="1" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
-    <col min="6" max="7" width="22" customWidth="1"/>
-    <col min="8" max="13" width="26" customWidth="1"/>
+    <col min="1" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="14" style="1" customWidth="1"/>
+    <col min="7" max="7" width="34" customWidth="1"/>
+    <col min="8" max="9" width="22" customWidth="1"/>
+    <col min="10" max="16" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -739,8 +787,11 @@
       <c r="K1"/>
       <c r="L1"/>
       <c r="M1"/>
-    </row>
-    <row r="2" ht="45" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1"/>
+      <c r="O1"/>
+      <c r="P1"/>
+    </row>
+    <row r="2" ht="45" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -762,10 +813,10 @@
       <c r="G2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="J2" s="4" t="s">
@@ -780,441 +831,513 @@
       <c r="M2" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="1">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="1">
         <v>46247</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" t="s">
+        <v>25</v>
+      </c>
+      <c r="P3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="1">
+        <v>46247</v>
+      </c>
+      <c r="G4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4" t="s">
+        <v>25</v>
+      </c>
+      <c r="O4" t="s">
+        <v>31</v>
+      </c>
+      <c r="P4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="1">
+        <v>46251</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O5" t="s">
+        <v>36</v>
+      </c>
+      <c r="P5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="4:16" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="1">
+        <v>46252</v>
+      </c>
+      <c r="G6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" t="s">
+        <v>42</v>
+      </c>
+      <c r="P6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>17</v>
       </c>
-      <c r="F3" t="s">
+      <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="1">
+        <v>46252</v>
+      </c>
+      <c r="G7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" t="s">
+        <v>49</v>
+      </c>
+      <c r="M7" t="s">
+        <v>25</v>
+      </c>
+      <c r="P7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
         <v>18</v>
       </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="C8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="1">
+        <v>46254</v>
+      </c>
+      <c r="G8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" t="s">
+        <v>24</v>
+      </c>
+      <c r="M8" t="s">
+        <v>25</v>
+      </c>
+      <c r="P8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="4:16" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" s="1">
+        <v>46259</v>
+      </c>
+      <c r="G9" t="s">
         <v>22</v>
       </c>
-      <c r="B4" t="s">
+      <c r="H9" t="s">
         <v>23</v>
       </c>
-      <c r="C4" t="s">
+      <c r="I9" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="1">
-        <v>46247</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="J9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M9" t="s">
         <v>25</v>
       </c>
-      <c r="F4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4" t="s">
-        <v>20</v>
-      </c>
-      <c r="M4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="1">
-        <v>46251</v>
-      </c>
-      <c r="E5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" t="s">
-        <v>20</v>
-      </c>
-      <c r="M5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="1">
+      <c r="O9" t="s">
+        <v>58</v>
+      </c>
+      <c r="P9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="4:16" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="1">
+        <v>46260</v>
+      </c>
+      <c r="G10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" t="s">
+        <v>63</v>
+      </c>
+      <c r="L10" t="s">
+        <v>64</v>
+      </c>
+      <c r="M10" t="s">
+        <v>25</v>
+      </c>
+      <c r="O10" t="s">
+        <v>65</v>
+      </c>
+      <c r="P10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F11" s="1">
+        <v>46240</v>
+      </c>
+      <c r="G11" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" t="s">
+        <v>73</v>
+      </c>
+      <c r="J11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L11" t="s">
+        <v>75</v>
+      </c>
+      <c r="M11" t="s">
+        <v>76</v>
+      </c>
+      <c r="N11" t="s">
+        <v>77</v>
+      </c>
+      <c r="P11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" t="s">
+        <v>80</v>
+      </c>
+      <c r="F12" s="1">
+        <v>46245</v>
+      </c>
+      <c r="G12" t="s">
+        <v>72</v>
+      </c>
+      <c r="H12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I12" t="s">
+        <v>73</v>
+      </c>
+      <c r="J12" t="s">
+        <v>81</v>
+      </c>
+      <c r="K12" t="s">
+        <v>82</v>
+      </c>
+      <c r="L12" t="s">
+        <v>75</v>
+      </c>
+      <c r="M12" t="s">
+        <v>76</v>
+      </c>
+      <c r="N12" t="s">
+        <v>77</v>
+      </c>
+      <c r="O12" t="s">
+        <v>83</v>
+      </c>
+      <c r="P12" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D13" t="s">
+        <v>87</v>
+      </c>
+      <c r="E13" t="s">
+        <v>88</v>
+      </c>
+      <c r="F13" s="1">
         <v>46252</v>
       </c>
-      <c r="E6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" t="s">
-        <v>35</v>
-      </c>
-      <c r="M6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" s="1">
-        <v>46252</v>
-      </c>
-      <c r="E7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" t="s">
-        <v>41</v>
-      </c>
-      <c r="K7" t="s">
-        <v>20</v>
-      </c>
-      <c r="M7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="1">
-        <v>46254</v>
-      </c>
-      <c r="E8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" t="s">
-        <v>19</v>
-      </c>
-      <c r="K8" t="s">
-        <v>20</v>
-      </c>
-      <c r="M8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="1">
+      <c r="G13" t="s">
+        <v>89</v>
+      </c>
+      <c r="H13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" t="s">
+        <v>73</v>
+      </c>
+      <c r="J13" t="s">
+        <v>90</v>
+      </c>
+      <c r="K13" t="s">
+        <v>91</v>
+      </c>
+      <c r="L13" t="s">
+        <v>92</v>
+      </c>
+      <c r="M13" t="s">
+        <v>76</v>
+      </c>
+      <c r="N13" t="s">
+        <v>77</v>
+      </c>
+      <c r="P13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" t="s">
+        <v>95</v>
+      </c>
+      <c r="E14" t="s">
+        <v>96</v>
+      </c>
+      <c r="F14" s="1">
+        <v>46258</v>
+      </c>
+      <c r="G14" t="s">
+        <v>97</v>
+      </c>
+      <c r="H14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I14" t="s">
+        <v>73</v>
+      </c>
+      <c r="J14" t="s">
+        <v>98</v>
+      </c>
+      <c r="K14" t="s">
+        <v>99</v>
+      </c>
+      <c r="L14" t="s">
+        <v>100</v>
+      </c>
+      <c r="M14" t="s">
+        <v>76</v>
+      </c>
+      <c r="N14" t="s">
+        <v>77</v>
+      </c>
+      <c r="P14" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" t="s">
+        <v>105</v>
+      </c>
+      <c r="E15" t="s">
+        <v>106</v>
+      </c>
+      <c r="F15" s="1">
         <v>46259</v>
       </c>
-      <c r="E9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" t="s">
-        <v>35</v>
-      </c>
-      <c r="K9" t="s">
-        <v>20</v>
-      </c>
-      <c r="M9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="1">
-        <v>46260</v>
-      </c>
-      <c r="E10" t="s">
-        <v>53</v>
-      </c>
-      <c r="F10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" t="s">
-        <v>54</v>
-      </c>
-      <c r="J10" t="s">
-        <v>55</v>
-      </c>
-      <c r="K10" t="s">
-        <v>20</v>
-      </c>
-      <c r="M10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>57</v>
-      </c>
-      <c r="B11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" t="s">
-        <v>59</v>
-      </c>
-      <c r="D11" s="1">
-        <v>46240</v>
-      </c>
-      <c r="E11" t="s">
-        <v>60</v>
-      </c>
-      <c r="F11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G11" t="s">
-        <v>61</v>
-      </c>
-      <c r="H11" t="s">
-        <v>62</v>
-      </c>
-      <c r="J11" t="s">
-        <v>63</v>
-      </c>
-      <c r="K11" t="s">
-        <v>64</v>
-      </c>
-      <c r="L11" t="s">
-        <v>65</v>
-      </c>
-      <c r="M11" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" s="1">
-        <v>46245</v>
-      </c>
-      <c r="E12" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12" t="s">
-        <v>18</v>
-      </c>
-      <c r="G12" t="s">
-        <v>61</v>
-      </c>
-      <c r="H12" t="s">
-        <v>69</v>
-      </c>
-      <c r="I12" t="s">
-        <v>70</v>
-      </c>
-      <c r="J12" t="s">
-        <v>63</v>
-      </c>
-      <c r="K12" t="s">
-        <v>64</v>
-      </c>
-      <c r="L12" t="s">
-        <v>65</v>
-      </c>
-      <c r="M12" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>72</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="G15" t="s">
+        <v>107</v>
+      </c>
+      <c r="H15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I15" t="s">
         <v>73</v>
       </c>
-      <c r="C13" t="s">
-        <v>74</v>
-      </c>
-      <c r="D13" s="1">
-        <v>46252</v>
-      </c>
-      <c r="E13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F13" t="s">
-        <v>18</v>
-      </c>
-      <c r="G13" t="s">
-        <v>61</v>
-      </c>
-      <c r="H13" t="s">
+      <c r="J15" t="s">
+        <v>108</v>
+      </c>
+      <c r="L15" t="s">
+        <v>109</v>
+      </c>
+      <c r="M15" t="s">
         <v>76</v>
       </c>
-      <c r="I13" t="s">
+      <c r="N15" t="s">
         <v>77</v>
       </c>
-      <c r="J13" t="s">
-        <v>78</v>
-      </c>
-      <c r="K13" t="s">
-        <v>64</v>
-      </c>
-      <c r="L13" t="s">
-        <v>65</v>
-      </c>
-      <c r="M13" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>80</v>
-      </c>
-      <c r="B14" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" t="s">
-        <v>82</v>
-      </c>
-      <c r="D14" s="1">
-        <v>46258</v>
-      </c>
-      <c r="E14" t="s">
-        <v>83</v>
-      </c>
-      <c r="F14" t="s">
-        <v>18</v>
-      </c>
-      <c r="G14" t="s">
-        <v>61</v>
-      </c>
-      <c r="H14" t="s">
-        <v>84</v>
-      </c>
-      <c r="I14" t="s">
-        <v>85</v>
-      </c>
-      <c r="J14" t="s">
-        <v>86</v>
-      </c>
-      <c r="K14" t="s">
-        <v>64</v>
-      </c>
-      <c r="L14" t="s">
-        <v>65</v>
-      </c>
-      <c r="M14" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>88</v>
-      </c>
-      <c r="B15" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" t="s">
-        <v>90</v>
-      </c>
-      <c r="D15" s="1">
-        <v>46259</v>
-      </c>
-      <c r="E15" t="s">
-        <v>91</v>
-      </c>
-      <c r="F15" t="s">
-        <v>18</v>
-      </c>
-      <c r="G15" t="s">
-        <v>61</v>
-      </c>
-      <c r="H15" t="s">
-        <v>92</v>
-      </c>
-      <c r="J15" t="s">
-        <v>93</v>
-      </c>
-      <c r="K15" t="s">
-        <v>64</v>
-      </c>
-      <c r="L15" t="s">
-        <v>65</v>
-      </c>
-      <c r="M15" t="s">
-        <v>94</v>
+      <c r="P15" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A1:P1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
